--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olympusssa-my.sharepoint.com/personal/10094312_olympus_com/Documents/デスクトップ/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10094312\Downloads\Doctor\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="11_F25DC773A252ABDACC10480481DA7EE65BDE58F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{237A7A4D-DBD0-43C0-AAE9-8D724DA4B949}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F3ED769-5915-401D-B440-A08A3FA843E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -166,38 +166,6 @@
     <t>去世</t>
     <phoneticPr fontId="1"/>
   </si>
-  <si>
-    <t>桂枝甘草汤</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>麻黄汤</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>风寒表实证</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>心阳虚</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>桂枝汤</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>风寒表虚证</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>麻杏石甘汤</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>肺热壅盛</t>
-    <phoneticPr fontId="1"/>
-  </si>
 </sst>
 </file>
 
@@ -280,10 +248,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -549,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="5.25" style="1" bestFit="1" customWidth="1"/>
@@ -560,7 +524,7 @@
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -577,7 +541,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
@@ -590,8 +554,11 @@
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -604,8 +571,11 @@
       <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -619,7 +589,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -636,7 +606,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
@@ -658,7 +628,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CE6F5-4C98-4917-9759-7DA81A6E4796}">
-  <dimension ref="A1:C295"/>
+  <dimension ref="A1:C296"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
@@ -667,1501 +637,1490 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>5</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>6</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>7</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>11</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>12</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>25</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B12" s="4"/>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>14</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B14" s="4"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>15</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>27</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B15" s="4"/>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>16</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B16" s="4"/>
     </row>
     <row r="17" spans="1:1">
       <c r="A17">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="229" spans="1:1">
       <c r="A229">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="237" spans="1:1">
       <c r="A237">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="238" spans="1:1">
       <c r="A238">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="252" spans="1:1">
       <c r="A252">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="253" spans="1:1">
       <c r="A253">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="254" spans="1:1">
       <c r="A254">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="257" spans="1:1">
       <c r="A257">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="258" spans="1:1">
       <c r="A258">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="259" spans="1:1">
       <c r="A259">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="262" spans="1:1">
       <c r="A262">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="263" spans="1:1">
       <c r="A263">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="265" spans="1:1">
       <c r="A265">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="274" spans="1:1">
       <c r="A274">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="275" spans="1:1">
       <c r="A275">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="276" spans="1:1">
       <c r="A276">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="277" spans="1:1">
       <c r="A277">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="278" spans="1:1">
       <c r="A278">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="279" spans="1:1">
       <c r="A279">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="282" spans="1:1">
       <c r="A282">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="285" spans="1:1">
       <c r="A285">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="286" spans="1:1">
       <c r="A286">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="290" spans="1:1">
       <c r="A290">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="293" spans="1:1">
       <c r="A293">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296">
         <v>295</v>
       </c>
     </row>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10094312\Downloads\Doctor\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300912AA-3957-4168-B56A-4D5B5FC8366E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210D9C5A-9390-42AA-96B6-EC42BDF6D1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -396,14 +396,17 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>发现药</t>
+      <t>雷万</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钧</t>
     </r>
     <r>
       <rPr>
@@ -413,33 +416,17 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>物</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>劣质</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>雷万</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>钧</t>
+      <t>奉命押送</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药</t>
     </r>
     <r>
       <rPr>
@@ -449,17 +436,48 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>奉命押送</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>药</t>
+      <t>材</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>雷万</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钧到处运送药材</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>发现药材以次充好</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>师爷送账本</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>杨善泉告知师爷被杀</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>库</t>
     </r>
     <r>
       <rPr>
@@ -469,23 +487,69 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>材</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>雷万</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>钧到处运送药材</t>
+      <t>房着火</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>杨善泉被烧死</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>杨素娘告知曹旺下落</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雷万钧去武昌府上告</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>找楚恭王帮忙</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>找到曹旺</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>证</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>物</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>证具在</t>
     </r>
     <phoneticPr fontId="1"/>
   </si>
@@ -1102,11 +1166,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.625" customWidth="1"/>
+    <col min="3" max="3" width="21.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1127,7 +1191,7 @@
         <v>46</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1142,8 +1206,8 @@
       <c r="A5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>52</v>
+      <c r="C5" s="5" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1151,32 +1215,62 @@
         <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
         <v>41</v>
       </c>
+      <c r="C7" s="4" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="C8" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="4" t="s">
         <v>43</v>
       </c>
+      <c r="C9" s="4" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="4" t="s">
         <v>48</v>
       </c>
+      <c r="C10" s="4" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="4" t="s">
         <v>44</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="C12" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="C13" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="C14" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10094312\Downloads\Doctor\Doctor\DataTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210D9C5A-9390-42AA-96B6-EC42BDF6D1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6443CB36-B2E6-4A52-B64A-F94CD6406666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="18900" windowHeight="10965" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="65">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -551,6 +551,14 @@
       </rPr>
       <t>证具在</t>
     </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>脾虚血瘀</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>肺络血瘀</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1115,16 +1123,20 @@
       <c r="C7" s="4"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="4"/>
+      <c r="A9" s="5"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="4"/>
+      <c r="A10" s="5"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="4"/>
+      <c r="A11" s="5" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="4"/>
+      <c r="A12" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="B12" s="4"/>
     </row>
     <row r="13" spans="1:3">

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6443CB36-B2E6-4A52-B64A-F94CD6406666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E554E06F-3169-4B1D-8060-82FEF34CDF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="18900" windowHeight="10965" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -551,14 +551,6 @@
       </rPr>
       <t>证具在</t>
     </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>脾虚血瘀</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>肺络血瘀</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -625,7 +617,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -633,11 +625,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -651,6 +658,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1129,14 +1137,10 @@
       <c r="A10" s="5"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="5" t="s">
-        <v>63</v>
-      </c>
+      <c r="A11" s="5"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="5" t="s">
-        <v>64</v>
-      </c>
+      <c r="A12" s="5"/>
       <c r="B12" s="4"/>
     </row>
     <row r="13" spans="1:3">
@@ -1146,6 +1150,7 @@
     <row r="14" spans="1:3">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
+      <c r="C14" s="7"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4"/>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E554E06F-3169-4B1D-8060-82FEF34CDF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C398C9-518B-493F-8DAA-70FD6E8D6A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="赈灾药材案" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -248,10 +248,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>楚恭王朱英𤈷</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>总旗雷万钧</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -550,6 +546,22 @@
         <charset val="134"/>
       </rPr>
       <t>证具在</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>楚恭王朱英</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="SimSun-ExtB"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>𤈷</t>
     </r>
     <phoneticPr fontId="1"/>
   </si>
@@ -558,7 +570,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -607,6 +619,13 @@
       <name val="Noto Sans JP"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun-ExtB"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1048,14 +1067,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CE6F5-4C98-4917-9759-7DA81A6E4796}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:8">
       <c r="A1" s="4" t="s">
         <v>20</v>
       </c>
@@ -1065,8 +1085,14 @@
       <c r="C1" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="F1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="4" t="s">
         <v>21</v>
       </c>
@@ -1076,8 +1102,14 @@
       <c r="C2" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="F2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="4" t="s">
         <v>24</v>
       </c>
@@ -1087,8 +1119,14 @@
       <c r="C3" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="F3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="4" t="s">
         <v>26</v>
       </c>
@@ -1096,10 +1134,16 @@
         <v>27</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>44</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="4" t="s">
         <v>28</v>
       </c>
@@ -1107,10 +1151,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>43</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="4" t="s">
         <v>31</v>
       </c>
@@ -1120,8 +1170,14 @@
       <c r="C6" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="F6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="6" t="s">
         <v>32</v>
       </c>
@@ -1129,34 +1185,72 @@
         <v>33</v>
       </c>
       <c r="C7" s="4"/>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="F7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="F8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="5"/>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="F9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="5"/>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="F10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="5"/>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="F11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="5"/>
       <c r="B12" s="4"/>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="H12" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="H13" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="7"/>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:8">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:8">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
     </row>
@@ -1183,114 +1277,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="15.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.375" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="C12" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="C13" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="C14" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C398C9-518B-493F-8DAA-70FD6E8D6A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2B1F54-22D5-4635-BDF7-82D139DA3B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -228,10 +228,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>富商</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>雷万钧</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -563,6 +559,10 @@
       </rPr>
       <t>𤈷</t>
     </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>贾荃</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -570,7 +570,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -959,7 +959,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="5.25" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
@@ -969,7 +969,7 @@
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -986,7 +986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
@@ -1068,31 +1068,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CE6F5-4C98-4917-9759-7DA81A6E4796}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>35</v>
+      <c r="C1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1">
+        <v>76</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>21</v>
       </c>
@@ -1100,16 +1103,19 @@
         <v>22</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
+      </c>
+      <c r="D2">
+        <v>92</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>24</v>
       </c>
@@ -1119,14 +1125,17 @@
       <c r="C3" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="D3">
+        <v>78</v>
+      </c>
       <c r="F3" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>26</v>
       </c>
@@ -1134,16 +1143,19 @@
         <v>27</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="D4">
+        <v>103</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>28</v>
       </c>
@@ -1151,16 +1163,19 @@
         <v>29</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="D5">
+        <v>40</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
         <v>31</v>
       </c>
@@ -1168,16 +1183,19 @@
         <v>30</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="D6">
+        <v>67</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
         <v>32</v>
       </c>
@@ -1186,87 +1204,87 @@
       </c>
       <c r="C7" s="4"/>
       <c r="F7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="F8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="F8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" s="5"/>
       <c r="F9" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" s="5"/>
       <c r="F10" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" s="5"/>
       <c r="F11" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" s="5"/>
       <c r="B12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="7"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" s="4"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" s="4"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" s="4"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" s="4"/>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" s="4"/>
     </row>
   </sheetData>
@@ -1278,7 +1296,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.375" bestFit="1" customWidth="1"/>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2B1F54-22D5-4635-BDF7-82D139DA3B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27C2E34-AEC7-4175-A41F-ED4B5434B0BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="65">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -563,6 +563,14 @@
   </si>
   <si>
     <t>贾荃</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>治愈世子</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世子</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1082,17 +1090,17 @@
       <c r="B1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>62</v>
+      <c r="C1" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="D1">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>61</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
@@ -1102,17 +1110,17 @@
       <c r="B2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>35</v>
+      <c r="C2" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="D2">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>45</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
@@ -1123,16 +1131,16 @@
         <v>25</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>44</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
@@ -1142,17 +1150,17 @@
       <c r="B4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>43</v>
+      <c r="C4" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>52</v>
+      <c r="H4" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -1163,16 +1171,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H5" t="s">
-        <v>51</v>
+      <c r="H5" s="5" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
@@ -1182,17 +1190,17 @@
       <c r="B6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>36</v>
+      <c r="C6" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="D6">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>53</v>
+      <c r="H6" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
@@ -1202,20 +1210,25 @@
       <c r="B7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="4"/>
+      <c r="C7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7">
+        <v>67</v>
+      </c>
       <c r="F7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>54</v>
+      <c r="H7" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="F8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>55</v>
+      <c r="H8" s="5" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
@@ -1224,7 +1237,7 @@
         <v>41</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
@@ -1233,7 +1246,7 @@
         <v>46</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
@@ -1242,27 +1255,30 @@
         <v>42</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" s="5"/>
       <c r="B12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="7"/>
+      <c r="H14" s="4" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" s="4"/>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27C2E34-AEC7-4175-A41F-ED4B5434B0BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE92CC9-9530-4DB7-97FE-CDF10AD1F997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -172,14 +172,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>肝阳上亢</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>大怒</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>大喜</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -225,10 +217,6 @@
   </si>
   <si>
     <t>师爷</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>雷万钧</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -571,6 +559,14 @@
   </si>
   <si>
     <t>世子</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>脾虚湿盛</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吴芷兰</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1085,191 +1081,187 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="D1">
         <v>55</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="C2" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D2">
         <v>76</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D3">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4">
+        <v>103</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D4">
-        <v>78</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="H4" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D5">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D7">
-        <v>67</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="H7" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="F8" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" s="5"/>
       <c r="F9" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A10" s="5"/>
+      <c r="A10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10">
+        <v>105</v>
+      </c>
       <c r="F10" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" s="5"/>
       <c r="F11" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" s="5"/>
       <c r="B12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
@@ -1277,7 +1269,7 @@
       <c r="B14" s="4"/>
       <c r="C14" s="7"/>
       <c r="H14" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE92CC9-9530-4DB7-97FE-CDF10AD1F997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55E8B39-744D-47EF-9F6F-6EA452EAA564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3270" yWindow="2490" windowWidth="18900" windowHeight="10905" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="赈灾药材案" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="支线剧情" sheetId="3" r:id="rId2"/>
+    <sheet name="赈灾药材案" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="68">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -172,10 +172,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>大喜</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>心脾两虚</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -205,14 +201,6 @@
   </si>
   <si>
     <t>心气虚</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>妊娠</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>泰山磐石散</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -566,7 +554,35 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>吴芷兰</t>
+    <t>肝阳上亢</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雷万钧</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>怒</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>喜</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>008</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>和尚肾精不足</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人参</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吴芷兰妊娠</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -667,7 +683,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -682,6 +698,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1070,8 +1087,45 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="4">
+        <v>105</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CE6F5-4C98-4917-9759-7DA81A6E4796}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -1080,237 +1134,233 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A1" s="4" t="s">
-        <v>62</v>
+      <c r="A1" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D1">
+        <v>43</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>58</v>
-      </c>
       <c r="H1" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D2">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="D3">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D4">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>39</v>
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>103</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6">
+      <c r="B8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8">
         <v>67</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="F9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="F7" s="4" t="s">
+      <c r="H9" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" s="5"/>
+      <c r="F10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="F11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="F8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A9" s="5"/>
-      <c r="F9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" s="4" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="H12" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10">
-        <v>105</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A11" s="5"/>
-      <c r="F11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A12" s="5"/>
-      <c r="B12" s="4"/>
-      <c r="H12" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A13" s="4"/>
+      <c r="A13" s="5"/>
       <c r="B13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
-      <c r="C14" s="7"/>
       <c r="H14" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
+      <c r="C15" s="7"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" s="4"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="B17" s="4"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" s="4"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" s="4"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" s="4"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" s="4"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A22" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55E8B39-744D-47EF-9F6F-6EA452EAA564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650706B1-00C0-4466-BB49-9E2C4BCAC6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3270" yWindow="2490" windowWidth="18900" windowHeight="10905" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="67">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -374,7 +374,32 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>钧</t>
+      <t>钧到处运送药材</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>发现药材以次充好</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>师爷送账本</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>杨善泉告知师爷被杀</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>库</t>
     </r>
     <r>
       <rPr>
@@ -384,17 +409,49 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>奉命押送</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>药</t>
+      <t>房着火</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>杨善泉被烧死</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>杨素娘告知曹旺下落</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雷万钧去武昌府上告</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>找楚恭王帮忙</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>找到曹旺</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>证</t>
     </r>
     <r>
       <rPr>
@@ -404,109 +461,6 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>材</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>雷万</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>钧到处运送药材</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>发现药材以次充好</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>师爷送账本</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>杨善泉告知师爷被杀</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>库</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>房着火</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>杨善泉被烧死</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>杨素娘告知曹旺下落</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>雷万钧去武昌府上告</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>找楚恭王帮忙</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>找到曹旺</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>人</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>证</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
       <t>物</t>
     </r>
     <r>
@@ -522,8 +476,56 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <r>
-      <t>楚恭王朱英</t>
+    <t>贾荃</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>治愈世子</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世子</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>脾虚湿盛</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>肝阳上亢</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雷万钧</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>怒</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>喜</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>008</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>和尚肾精不足</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人参</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吴芷兰妊娠</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>楚王朱英</t>
     </r>
     <r>
       <rPr>
@@ -535,54 +537,6 @@
       </rPr>
       <t>𤈷</t>
     </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>贾荃</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>治愈世子</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>世子</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>脾虚湿盛</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>肝阳上亢</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>雷万钧</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>怒</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>喜</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>008</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>和尚肾精不足</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>人参</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>吴芷兰妊娠</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1099,10 +1053,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C1">
         <v>98</v>
@@ -1110,7 +1064,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C2" s="4">
         <v>105</v>
@@ -1135,27 +1089,27 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D1">
         <v>43</v>
       </c>
       <c r="F1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D2">
         <v>55</v>
@@ -1169,13 +1123,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="C3" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D3">
         <v>92</v>
@@ -1184,7 +1138,7 @@
         <v>38</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
@@ -1192,10 +1146,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D4">
         <v>76</v>
@@ -1203,8 +1157,8 @@
       <c r="F4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>43</v>
+      <c r="H4" s="5" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -1223,8 +1177,8 @@
       <c r="F5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>46</v>
+      <c r="H5" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
@@ -1243,8 +1197,8 @@
       <c r="F6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H6" t="s">
-        <v>45</v>
+      <c r="H6" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
@@ -1264,7 +1218,7 @@
         <v>33</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
@@ -1283,16 +1237,16 @@
       <c r="F8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>48</v>
+      <c r="H8" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="F9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>49</v>
+      <c r="H9" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
@@ -1301,7 +1255,7 @@
         <v>40</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
@@ -1309,7 +1263,7 @@
         <v>36</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
@@ -1327,9 +1281,6 @@
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
-      <c r="H14" s="4" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" s="4"/>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650706B1-00C0-4466-BB49-9E2C4BCAC6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1971DF07-71C2-4283-8F49-2A99F770A7E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -505,10 +505,6 @@
   </si>
   <si>
     <t>喜</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>008</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1052,11 +1048,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="8"/>
+      <c r="B1" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="C1">
         <v>98</v>
@@ -1064,7 +1058,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" s="4">
         <v>105</v>
@@ -1089,7 +1083,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>54</v>
@@ -1098,7 +1092,7 @@
         <v>43</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>55</v>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1971DF07-71C2-4283-8F49-2A99F770A7E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C8C80A-32AD-40DD-943D-E496E9D014DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="支线剧情" sheetId="3" r:id="rId2"/>
-    <sheet name="赈灾药材案" sheetId="2" r:id="rId3"/>
+    <sheet name="时间线" sheetId="1" r:id="rId1"/>
+    <sheet name="赈灾药材案" sheetId="2" r:id="rId2"/>
+    <sheet name="支线剧情" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="76">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -168,66 +168,61 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>痰火扰心</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>心脾两虚</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>思虑过度</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>肾气不固</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>恐</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>肺气虚</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>悲伤过度</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>惊</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>心气虚</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>师爷</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>看门</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>知州吴世良</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>师爷沈修文</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>总旗雷万钧</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>管家赵顺</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
+    <t>和尚肾精不足</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吴芷兰妊娠</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>006</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>005</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>007</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>008</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>014</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>017</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世子脾虚湿盛</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>贾荃兜售人参</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雷万钧肝阳上亢</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>贾荃痰火</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -236,7 +231,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>库</t>
+      <t>扰</t>
     </r>
     <r>
       <rPr>
@@ -246,8 +241,15 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>大使</t>
-    </r>
+      <t>心</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>师爷心脾两虚</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -256,31 +258,152 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>杨善泉</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>杨素娘</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>杨善泉</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>按察使</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>布政使</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>看守曹旺</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
+      <t>杨善泉肾</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>气不固</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>知州有请</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>药材到货</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>药材有假</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>孙大夫被抓</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雷万钧来访</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>009</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>010</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>011</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>012</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>013</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>009+1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>010+1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>011+1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>012+1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>016+1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>014+1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>库房失火</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>赵顺来访</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夜晚遇刺</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>结案</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>015</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>016</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>018</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>019</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>020</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>021</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雷万钧归来</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>沈修文来访</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>017+1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>018+1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>019+1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>020+2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>107全解</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -289,250 +412,36 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>药</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>商</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>贾荃</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>贾</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>荃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>到蕲州</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>知州</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>召见分发药材</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>雷万</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>钧到处运送药材</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>发现药材以次充好</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>师爷送账本</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>杨善泉告知师爷被杀</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>库</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>房着火</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>杨善泉被烧死</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>杨素娘告知曹旺下落</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>雷万钧去武昌府上告</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>找楚恭王帮忙</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>找到曹旺</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>人</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>证</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>物</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>证具在</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>贾荃</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>治愈世子</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>世子</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>脾虚湿盛</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>肝阳上亢</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>雷万钧</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>怒</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>喜</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>和尚肾精不足</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>人参</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>吴芷兰妊娠</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>楚王朱英</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="SimSun-ExtB"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>𤈷</t>
-    </r>
+      <t>锁</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>013+1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>015+3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>022</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>解锁心得</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前置剧情</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -540,7 +449,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -572,30 +481,9 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Microsoft YaHei"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Noto Sans JP"/>
       <family val="3"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="SimSun-ExtB"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -633,7 +521,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -646,9 +534,17 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1037,33 +933,270 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
-  <dimension ref="A1:D2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CE6F5-4C98-4917-9759-7DA81A6E4796}">
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" s="8"/>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A1" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="B1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="8">
+        <v>43</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="G2" s="4"/>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="8">
+        <v>55</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="G3" s="4"/>
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="8">
+        <v>92</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="8">
+        <v>76</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="G5" s="4"/>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="I8" s="4"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A9" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A10" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="8">
+        <v>78</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A12" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C1">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B2" s="6" t="s">
+      <c r="C12" s="8"/>
+      <c r="D12" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A13" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="8">
+        <v>103</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I14" s="4"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A15" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="4">
-        <v>105</v>
-      </c>
-      <c r="D2" s="4"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A16" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A17" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A18" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A19" s="6"/>
+      <c r="B19" s="4"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A20" s="6"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A21" s="6"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A22" s="6"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A23" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1072,237 +1205,62 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CE6F5-4C98-4917-9759-7DA81A6E4796}">
-  <dimension ref="A1:H22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1">
-        <v>43</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2">
-        <v>55</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A3" s="4" t="s">
-        <v>58</v>
-      </c>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="8">
+        <v>98</v>
+      </c>
+      <c r="D2" s="8"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" s="6"/>
       <c r="B3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3">
-        <v>92</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="8">
+        <v>105</v>
+      </c>
+      <c r="D3" s="8"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="6"/>
+      <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4">
-        <v>76</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A5" s="4" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" s="6"/>
+      <c r="B5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5">
-        <v>78</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6">
-        <v>103</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7">
-        <v>40</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8">
-        <v>67</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="F9" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A10" s="5"/>
-      <c r="F10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="F11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="H12" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A13" s="5"/>
-      <c r="B13" s="4"/>
-      <c r="H13" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="7"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A18" s="4"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A19" s="4"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A20" s="4"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A21" s="4"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A22" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C8C80A-32AD-40DD-943D-E496E9D014DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792F8333-ADF3-42D1-9147-898C4A609E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="77">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -442,6 +442,10 @@
   </si>
   <si>
     <t>前置剧情</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>023</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1241,7 +1245,9 @@
       <c r="D2" s="8"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A3" s="6"/>
+      <c r="A3" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="B3" s="4" t="s">
         <v>23</v>
       </c>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792F8333-ADF3-42D1-9147-898C4A609E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245F8427-0811-4372-B056-44885FE7BC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245F8427-0811-4372-B056-44885FE7BC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7699757-5545-4D0E-B3CA-A5C01C671B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2370" yWindow="1995" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>
@@ -22,23 +22,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="78">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -448,22 +437,26 @@
     <t>023</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>肺阴虚</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -551,7 +544,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -830,17 +823,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="5.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.265625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.46484375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -857,7 +850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="18">
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
@@ -871,7 +864,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="18">
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -885,7 +878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="18">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -899,7 +892,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="18">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -916,7 +909,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" ht="18">
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
@@ -939,16 +932,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CE6F5-4C98-4917-9759-7DA81A6E4796}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="7" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1328125" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" ht="18">
       <c r="A1" s="6" t="s">
         <v>72</v>
       </c>
@@ -962,7 +955,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" ht="18">
       <c r="A2" s="6" t="s">
         <v>24</v>
       </c>
@@ -976,7 +969,7 @@
       <c r="G2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="18">
       <c r="A3" s="6" t="s">
         <v>25</v>
       </c>
@@ -990,7 +983,7 @@
       <c r="G3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" ht="18">
       <c r="A4" s="6" t="s">
         <v>26</v>
       </c>
@@ -1004,7 +997,7 @@
       <c r="G4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" ht="18">
       <c r="A5" s="6" t="s">
         <v>27</v>
       </c>
@@ -1018,7 +1011,7 @@
       <c r="G5" s="4"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" ht="18">
       <c r="A6" s="6" t="s">
         <v>41</v>
       </c>
@@ -1031,7 +1024,7 @@
       <c r="D6" s="8"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" ht="18">
       <c r="A7" s="6" t="s">
         <v>42</v>
       </c>
@@ -1044,7 +1037,7 @@
       <c r="G7" s="4"/>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="18">
       <c r="A8" s="6" t="s">
         <v>43</v>
       </c>
@@ -1057,7 +1050,7 @@
       <c r="G8" s="4"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" ht="18">
       <c r="A9" s="6" t="s">
         <v>44</v>
       </c>
@@ -1070,7 +1063,7 @@
       <c r="G9" s="4"/>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" ht="18">
       <c r="A10" s="6" t="s">
         <v>45</v>
       </c>
@@ -1083,7 +1076,7 @@
       <c r="G10" s="4"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" ht="18">
       <c r="A11" s="6" t="s">
         <v>28</v>
       </c>
@@ -1099,7 +1092,7 @@
       <c r="G11" s="4"/>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" ht="18">
       <c r="A12" s="6" t="s">
         <v>56</v>
       </c>
@@ -1113,7 +1106,7 @@
       <c r="G12" s="4"/>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" ht="18">
       <c r="A13" s="6" t="s">
         <v>57</v>
       </c>
@@ -1126,7 +1119,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" ht="18">
       <c r="A14" s="6" t="s">
         <v>29</v>
       </c>
@@ -1141,7 +1134,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" ht="18">
       <c r="A15" s="6" t="s">
         <v>58</v>
       </c>
@@ -1152,7 +1145,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:9" ht="18">
       <c r="A16" s="6" t="s">
         <v>59</v>
       </c>
@@ -1164,7 +1157,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" ht="18">
       <c r="A17" s="6" t="s">
         <v>60</v>
       </c>
@@ -1175,7 +1168,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" ht="18">
       <c r="A18" s="6" t="s">
         <v>61</v>
       </c>
@@ -1186,20 +1179,20 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" ht="18">
       <c r="A19" s="6"/>
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" ht="18">
       <c r="A20" s="6"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" ht="18">
       <c r="A21" s="6"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" ht="18">
       <c r="A22" s="6"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" ht="18">
       <c r="A23" s="6"/>
     </row>
   </sheetData>
@@ -1210,15 +1203,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="18">
       <c r="A1" s="4" t="s">
         <v>72</v>
       </c>
@@ -1232,39 +1225,56 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:4" ht="18">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="8">
+        <v>40</v>
+      </c>
+      <c r="D2" s="8"/>
+    </row>
+    <row r="3" spans="1:4" ht="18">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="8">
+        <v>44</v>
+      </c>
+      <c r="D3" s="8"/>
+    </row>
+    <row r="4" spans="1:4" ht="18">
+      <c r="A4" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C4" s="8">
         <v>98</v>
       </c>
-      <c r="D2" s="8"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="18">
+      <c r="A5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C5" s="8">
         <v>105</v>
       </c>
-      <c r="D3" s="8"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A4" s="6"/>
-      <c r="B4" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A5" s="6"/>
-      <c r="B5" s="4" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="18">
+      <c r="A9" s="6"/>
+    </row>
+    <row r="10" spans="1:4" ht="18">
+      <c r="A10" s="6"/>
+    </row>
+    <row r="11" spans="1:4" ht="18">
+      <c r="B11" s="4" t="s">
         <v>21</v>
       </c>
     </row>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7699757-5545-4D0E-B3CA-A5C01C671B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D5EFF1-E9A2-4B26-8A65-91FA785F1B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2370" yWindow="1995" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -414,10 +425,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>022</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>剧情ID</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -434,11 +441,15 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>023</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>肺阴虚</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>温燥证</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>天数</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -446,17 +457,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -544,7 +555,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -823,17 +834,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="5.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.25" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.46484375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -850,7 +861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
@@ -864,7 +875,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -878,7 +889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -892,7 +903,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -909,7 +920,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
@@ -932,30 +943,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CE6F5-4C98-4917-9759-7DA81A6E4796}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="7" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.125" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="18">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>24</v>
       </c>
@@ -969,7 +980,7 @@
       <c r="G2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" ht="18">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>25</v>
       </c>
@@ -983,7 +994,7 @@
       <c r="G3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" ht="18">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
         <v>26</v>
       </c>
@@ -997,7 +1008,7 @@
       <c r="G4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" ht="18">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" s="6" t="s">
         <v>27</v>
       </c>
@@ -1011,7 +1022,7 @@
       <c r="G5" s="4"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9" ht="18">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>41</v>
       </c>
@@ -1024,7 +1035,7 @@
       <c r="D6" s="8"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:9" ht="18">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
         <v>42</v>
       </c>
@@ -1037,7 +1048,7 @@
       <c r="G7" s="4"/>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9" ht="18">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="6" t="s">
         <v>43</v>
       </c>
@@ -1050,7 +1061,7 @@
       <c r="G8" s="4"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" ht="18">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="6" t="s">
         <v>44</v>
       </c>
@@ -1063,7 +1074,7 @@
       <c r="G9" s="4"/>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:9" ht="18">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="6" t="s">
         <v>45</v>
       </c>
@@ -1076,7 +1087,7 @@
       <c r="G10" s="4"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:9" ht="18">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="6" t="s">
         <v>28</v>
       </c>
@@ -1092,7 +1103,7 @@
       <c r="G11" s="4"/>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9" ht="18">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
         <v>56</v>
       </c>
@@ -1106,7 +1117,7 @@
       <c r="G12" s="4"/>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9" ht="18">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" s="6" t="s">
         <v>57</v>
       </c>
@@ -1119,7 +1130,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9" ht="18">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" s="6" t="s">
         <v>29</v>
       </c>
@@ -1134,7 +1145,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9" ht="18">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A15" s="6" t="s">
         <v>58</v>
       </c>
@@ -1145,7 +1156,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="18">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" s="6" t="s">
         <v>59</v>
       </c>
@@ -1157,7 +1168,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" s="6" t="s">
         <v>60</v>
       </c>
@@ -1168,7 +1179,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" s="6" t="s">
         <v>61</v>
       </c>
@@ -1179,20 +1190,20 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="18">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" s="6"/>
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="18">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" s="6"/>
     </row>
-    <row r="21" spans="1:4" ht="18">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" s="6"/>
     </row>
-    <row r="22" spans="1:4" ht="18">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" s="6"/>
     </row>
-    <row r="23" spans="1:4" ht="18">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" s="6"/>
     </row>
   </sheetData>
@@ -1203,78 +1214,88 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A1" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" s="8">
+        <v>22</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" s="8">
+        <v>23</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" s="8">
+        <v>24</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="18">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="8">
-        <v>40</v>
-      </c>
-      <c r="D2" s="8"/>
-    </row>
-    <row r="3" spans="1:4" ht="18">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" s="8">
+      <c r="C4" s="8">
         <v>44</v>
       </c>
-      <c r="D3" s="8"/>
-    </row>
-    <row r="4" spans="1:4" ht="18">
-      <c r="A4" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="8" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" s="8">
+        <v>25</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C5" s="8">
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18">
-      <c r="A5" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="8" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" s="8">
+        <v>26</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C6" s="8">
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18">
-      <c r="A9" s="6"/>
-    </row>
-    <row r="10" spans="1:4" ht="18">
-      <c r="A10" s="6"/>
-    </row>
-    <row r="11" spans="1:4" ht="18">
-      <c r="B11" s="4" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B11" s="8" t="s">
         <v>21</v>
       </c>
     </row>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D5EFF1-E9A2-4B26-8A65-91FA785F1B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9843BF6C-FAA4-430B-8EF8-F1EA5233664C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14317" yWindow="0" windowWidth="14565" windowHeight="15563" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>
@@ -457,17 +457,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -555,7 +555,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -834,17 +834,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="5.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.265625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.46484375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -861,7 +861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="18">
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
@@ -875,7 +875,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="18">
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -889,7 +889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="18">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -903,7 +903,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="18">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -920,7 +920,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" ht="18">
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
@@ -943,16 +943,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CE6F5-4C98-4917-9759-7DA81A6E4796}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="7" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1328125" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" ht="18">
       <c r="A1" s="6" t="s">
         <v>71</v>
       </c>
@@ -966,7 +966,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" ht="18">
       <c r="A2" s="6" t="s">
         <v>24</v>
       </c>
@@ -980,7 +980,7 @@
       <c r="G2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="18">
       <c r="A3" s="6" t="s">
         <v>25</v>
       </c>
@@ -994,7 +994,7 @@
       <c r="G3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" ht="18">
       <c r="A4" s="6" t="s">
         <v>26</v>
       </c>
@@ -1008,7 +1008,7 @@
       <c r="G4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" ht="18">
       <c r="A5" s="6" t="s">
         <v>27</v>
       </c>
@@ -1022,7 +1022,7 @@
       <c r="G5" s="4"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" ht="18">
       <c r="A6" s="6" t="s">
         <v>41</v>
       </c>
@@ -1035,7 +1035,7 @@
       <c r="D6" s="8"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" ht="18">
       <c r="A7" s="6" t="s">
         <v>42</v>
       </c>
@@ -1048,7 +1048,7 @@
       <c r="G7" s="4"/>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="18">
       <c r="A8" s="6" t="s">
         <v>43</v>
       </c>
@@ -1061,7 +1061,7 @@
       <c r="G8" s="4"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" ht="18">
       <c r="A9" s="6" t="s">
         <v>44</v>
       </c>
@@ -1074,7 +1074,7 @@
       <c r="G9" s="4"/>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" ht="18">
       <c r="A10" s="6" t="s">
         <v>45</v>
       </c>
@@ -1087,7 +1087,7 @@
       <c r="G10" s="4"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" ht="18">
       <c r="A11" s="6" t="s">
         <v>28</v>
       </c>
@@ -1103,7 +1103,7 @@
       <c r="G11" s="4"/>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" ht="18">
       <c r="A12" s="6" t="s">
         <v>56</v>
       </c>
@@ -1117,7 +1117,7 @@
       <c r="G12" s="4"/>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" ht="18">
       <c r="A13" s="6" t="s">
         <v>57</v>
       </c>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" ht="18">
       <c r="A14" s="6" t="s">
         <v>29</v>
       </c>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" ht="18">
       <c r="A15" s="6" t="s">
         <v>58</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:9" ht="18">
       <c r="A16" s="6" t="s">
         <v>59</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" ht="18">
       <c r="A17" s="6" t="s">
         <v>60</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" ht="18">
       <c r="A18" s="6" t="s">
         <v>61</v>
       </c>
@@ -1190,20 +1190,20 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" ht="18">
       <c r="A19" s="6"/>
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" ht="18">
       <c r="A20" s="6"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" ht="18">
       <c r="A21" s="6"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" ht="18">
       <c r="A22" s="6"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" ht="18">
       <c r="A23" s="6"/>
     </row>
   </sheetData>
@@ -1215,14 +1215,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="7.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1328125" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5">
       <c r="A1" s="8" t="s">
         <v>71</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5">
       <c r="A2" s="8">
         <v>22</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5">
       <c r="A3" s="8">
         <v>23</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5">
       <c r="A4" s="8">
         <v>24</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5">
       <c r="A5" s="8">
         <v>25</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5">
       <c r="A6" s="8">
         <v>26</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5">
       <c r="B11" s="8" t="s">
         <v>21</v>
       </c>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9843BF6C-FAA4-430B-8EF8-F1EA5233664C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9CD996-DA81-48F7-930F-00FC981C1D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14317" yWindow="0" windowWidth="14565" windowHeight="15563" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2708" yWindow="2332" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>
@@ -21,17 +21,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -974,7 +963,7 @@
         <v>31</v>
       </c>
       <c r="C2" s="8">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D2" s="5"/>
       <c r="G2" s="4"/>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9CD996-DA81-48F7-930F-00FC981C1D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C1FBAE-C181-466A-BDEE-789ED636B44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2708" yWindow="2332" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -1,33 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C1FBAE-C181-466A-BDEE-789ED636B44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08149B4C-BFF4-45D8-8663-E9E510F0DD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2708" yWindow="2332" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>
     <sheet name="赈灾药材案" sheetId="2" r:id="rId2"/>
     <sheet name="支线剧情" sheetId="3" r:id="rId3"/>
+    <sheet name="收入" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="100">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -441,22 +453,192 @@
     <t>天数</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>名望</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初窥门径</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>略有小成</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>融会贯通</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>炉火纯青</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出神入化</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>诊费</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>药费</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0~100</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>101~300</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>陈皮半夏工钱</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>柴火</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>粮食</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>衣服</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>随礼</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>税</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1~</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>301~</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>600</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1~</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2000</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>~</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>400</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>300~2000</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>888~8888</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -481,6 +663,20 @@
       <name val="Noto Sans JP"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei UI"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -518,7 +714,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -542,9 +738,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -823,17 +1023,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="5.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.25" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.46484375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -850,7 +1050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
@@ -864,7 +1064,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -878,7 +1078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -892,7 +1092,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -909,7 +1109,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
@@ -932,16 +1132,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CE6F5-4C98-4917-9759-7DA81A6E4796}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="7" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.125" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
         <v>71</v>
       </c>
@@ -955,7 +1155,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="18">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>24</v>
       </c>
@@ -969,7 +1169,7 @@
       <c r="G2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" ht="18">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>25</v>
       </c>
@@ -983,7 +1183,7 @@
       <c r="G3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" ht="18">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
         <v>26</v>
       </c>
@@ -997,7 +1197,7 @@
       <c r="G4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" ht="18">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" s="6" t="s">
         <v>27</v>
       </c>
@@ -1011,7 +1211,7 @@
       <c r="G5" s="4"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9" ht="18">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>41</v>
       </c>
@@ -1024,7 +1224,7 @@
       <c r="D6" s="8"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:9" ht="18">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
         <v>42</v>
       </c>
@@ -1037,7 +1237,7 @@
       <c r="G7" s="4"/>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9" ht="18">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="6" t="s">
         <v>43</v>
       </c>
@@ -1050,7 +1250,7 @@
       <c r="G8" s="4"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" ht="18">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="6" t="s">
         <v>44</v>
       </c>
@@ -1063,7 +1263,7 @@
       <c r="G9" s="4"/>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:9" ht="18">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="6" t="s">
         <v>45</v>
       </c>
@@ -1076,7 +1276,7 @@
       <c r="G10" s="4"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:9" ht="18">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="6" t="s">
         <v>28</v>
       </c>
@@ -1092,7 +1292,7 @@
       <c r="G11" s="4"/>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9" ht="18">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
         <v>56</v>
       </c>
@@ -1106,7 +1306,7 @@
       <c r="G12" s="4"/>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9" ht="18">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" s="6" t="s">
         <v>57</v>
       </c>
@@ -1119,7 +1319,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9" ht="18">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" s="6" t="s">
         <v>29</v>
       </c>
@@ -1134,7 +1334,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9" ht="18">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A15" s="6" t="s">
         <v>58</v>
       </c>
@@ -1145,7 +1345,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="18">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" s="6" t="s">
         <v>59</v>
       </c>
@@ -1157,7 +1357,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" s="6" t="s">
         <v>60</v>
       </c>
@@ -1168,7 +1368,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" s="6" t="s">
         <v>61</v>
       </c>
@@ -1179,20 +1379,20 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="18">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" s="6"/>
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="18">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" s="6"/>
     </row>
-    <row r="21" spans="1:4" ht="18">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" s="6"/>
     </row>
-    <row r="22" spans="1:4" ht="18">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" s="6"/>
     </row>
-    <row r="23" spans="1:4" ht="18">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" s="6"/>
     </row>
   </sheetData>
@@ -1204,14 +1404,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="7.1328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.125" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>71</v>
       </c>
@@ -1228,7 +1428,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" s="8">
         <v>22</v>
       </c>
@@ -1239,7 +1439,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="8">
         <v>23</v>
       </c>
@@ -1250,7 +1450,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" s="8">
         <v>24</v>
       </c>
@@ -1261,7 +1461,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="8">
         <v>25</v>
       </c>
@@ -1272,7 +1472,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" s="8">
         <v>26</v>
       </c>
@@ -1283,9 +1483,132 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B11" s="8" t="s">
         <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00DA8846-409D-4B70-B280-9B5D3F94AB77}">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9" style="4"/>
+    <col min="2" max="2" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="9" style="4"/>
+    <col min="7" max="7" width="13" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="12"/>
+    <col min="9" max="16384" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B1" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="4">
+        <v>10</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H2" s="12">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="4">
+        <v>50</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3" s="12">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="4">
+        <v>200</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="H4" s="12">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="4">
+        <v>500</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G7" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08149B4C-BFF4-45D8-8663-E9E510F0DD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A6C7D7-9D93-44AA-87C9-C25E32A3D46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A6C7D7-9D93-44AA-87C9-C25E32A3D46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9762C27D-8FC4-44E2-8580-3F85FD3B3A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2430" yWindow="4057" windowWidth="21600" windowHeight="11423" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>
@@ -628,17 +628,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -714,7 +714,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -742,9 +742,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1023,17 +1025,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="5.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.265625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.46484375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1050,7 +1052,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="18">
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1064,7 +1066,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="18">
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1078,7 +1080,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="18">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1092,7 +1094,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="18">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1109,7 +1111,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" ht="18">
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
@@ -1132,16 +1134,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CE6F5-4C98-4917-9759-7DA81A6E4796}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="7" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1328125" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" ht="18">
       <c r="A1" s="6" t="s">
         <v>71</v>
       </c>
@@ -1155,7 +1157,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" ht="18">
       <c r="A2" s="6" t="s">
         <v>24</v>
       </c>
@@ -1169,7 +1171,7 @@
       <c r="G2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="18">
       <c r="A3" s="6" t="s">
         <v>25</v>
       </c>
@@ -1183,7 +1185,7 @@
       <c r="G3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" ht="18">
       <c r="A4" s="6" t="s">
         <v>26</v>
       </c>
@@ -1197,7 +1199,7 @@
       <c r="G4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" ht="18">
       <c r="A5" s="6" t="s">
         <v>27</v>
       </c>
@@ -1211,7 +1213,7 @@
       <c r="G5" s="4"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" ht="18">
       <c r="A6" s="6" t="s">
         <v>41</v>
       </c>
@@ -1224,7 +1226,7 @@
       <c r="D6" s="8"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" ht="18">
       <c r="A7" s="6" t="s">
         <v>42</v>
       </c>
@@ -1237,7 +1239,7 @@
       <c r="G7" s="4"/>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="18">
       <c r="A8" s="6" t="s">
         <v>43</v>
       </c>
@@ -1250,7 +1252,7 @@
       <c r="G8" s="4"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" ht="18">
       <c r="A9" s="6" t="s">
         <v>44</v>
       </c>
@@ -1263,7 +1265,7 @@
       <c r="G9" s="4"/>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" ht="18">
       <c r="A10" s="6" t="s">
         <v>45</v>
       </c>
@@ -1276,7 +1278,7 @@
       <c r="G10" s="4"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" ht="18">
       <c r="A11" s="6" t="s">
         <v>28</v>
       </c>
@@ -1292,7 +1294,7 @@
       <c r="G11" s="4"/>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" ht="18">
       <c r="A12" s="6" t="s">
         <v>56</v>
       </c>
@@ -1306,7 +1308,7 @@
       <c r="G12" s="4"/>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" ht="18">
       <c r="A13" s="6" t="s">
         <v>57</v>
       </c>
@@ -1319,7 +1321,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" ht="18">
       <c r="A14" s="6" t="s">
         <v>29</v>
       </c>
@@ -1334,7 +1336,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" ht="18">
       <c r="A15" s="6" t="s">
         <v>58</v>
       </c>
@@ -1345,7 +1347,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:9" ht="18">
       <c r="A16" s="6" t="s">
         <v>59</v>
       </c>
@@ -1357,7 +1359,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" ht="18">
       <c r="A17" s="6" t="s">
         <v>60</v>
       </c>
@@ -1368,7 +1370,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" ht="18">
       <c r="A18" s="6" t="s">
         <v>61</v>
       </c>
@@ -1379,20 +1381,20 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" ht="18">
       <c r="A19" s="6"/>
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" ht="18">
       <c r="A20" s="6"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" ht="18">
       <c r="A21" s="6"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" ht="18">
       <c r="A22" s="6"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" ht="18">
       <c r="A23" s="6"/>
     </row>
   </sheetData>
@@ -1404,14 +1406,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="7.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1328125" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5">
       <c r="A1" s="8" t="s">
         <v>71</v>
       </c>
@@ -1428,7 +1430,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5">
       <c r="A2" s="8">
         <v>22</v>
       </c>
@@ -1439,7 +1441,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5">
       <c r="A3" s="8">
         <v>23</v>
       </c>
@@ -1450,7 +1452,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5">
       <c r="A4" s="8">
         <v>24</v>
       </c>
@@ -1461,7 +1463,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5">
       <c r="A5" s="8">
         <v>25</v>
       </c>
@@ -1472,7 +1474,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5">
       <c r="A6" s="8">
         <v>26</v>
       </c>
@@ -1483,7 +1485,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5">
       <c r="B11" s="8" t="s">
         <v>21</v>
       </c>
@@ -1496,36 +1498,37 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00DA8846-409D-4B70-B280-9B5D3F94AB77}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
-    <col min="2" max="2" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="9" style="4"/>
     <col min="7" max="7" width="13" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="12"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B1" s="4" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="13"/>
+      <c r="B1" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="13" t="s">
         <v>84</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:8">
+      <c r="A2" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="13">
         <v>10</v>
       </c>
       <c r="G2" s="4" t="s">
@@ -1535,14 +1538,14 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:8">
+      <c r="A3" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="13">
         <v>50</v>
       </c>
       <c r="G3" s="4" t="s">
@@ -1552,14 +1555,14 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:8">
+      <c r="A4" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="13">
         <v>200</v>
       </c>
       <c r="G4" s="11" t="s">
@@ -1569,14 +1572,14 @@
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:8">
+      <c r="A5" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="13">
         <v>500</v>
       </c>
       <c r="G5" s="4" t="s">
@@ -1586,14 +1589,14 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:8">
+      <c r="A6" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="13">
         <v>1000</v>
       </c>
       <c r="G6" s="4" t="s">
@@ -1603,16 +1606,20 @@
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="G7" s="4" t="s">
         <v>92</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>99</v>
       </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="B10" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9762C27D-8FC4-44E2-8580-3F85FD3B3A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FA989B-8E8D-4FB9-A175-1A051FF98F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2430" yWindow="4057" windowWidth="21600" windowHeight="11423" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="99">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -514,10 +514,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>税</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -628,17 +624,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -746,7 +742,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1025,17 +1021,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="5.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.25" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.46484375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1052,7 +1048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1066,7 +1062,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1080,7 +1076,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1094,7 +1090,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1111,7 +1107,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
@@ -1134,16 +1130,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CE6F5-4C98-4917-9759-7DA81A6E4796}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="7" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.125" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
         <v>71</v>
       </c>
@@ -1157,7 +1153,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="18">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>24</v>
       </c>
@@ -1171,7 +1167,7 @@
       <c r="G2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" ht="18">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>25</v>
       </c>
@@ -1185,7 +1181,7 @@
       <c r="G3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" ht="18">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
         <v>26</v>
       </c>
@@ -1199,7 +1195,7 @@
       <c r="G4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" ht="18">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" s="6" t="s">
         <v>27</v>
       </c>
@@ -1213,7 +1209,7 @@
       <c r="G5" s="4"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9" ht="18">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>41</v>
       </c>
@@ -1226,7 +1222,7 @@
       <c r="D6" s="8"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:9" ht="18">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
         <v>42</v>
       </c>
@@ -1239,7 +1235,7 @@
       <c r="G7" s="4"/>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9" ht="18">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="6" t="s">
         <v>43</v>
       </c>
@@ -1252,7 +1248,7 @@
       <c r="G8" s="4"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" ht="18">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="6" t="s">
         <v>44</v>
       </c>
@@ -1265,7 +1261,7 @@
       <c r="G9" s="4"/>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:9" ht="18">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="6" t="s">
         <v>45</v>
       </c>
@@ -1278,7 +1274,7 @@
       <c r="G10" s="4"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:9" ht="18">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="6" t="s">
         <v>28</v>
       </c>
@@ -1294,7 +1290,7 @@
       <c r="G11" s="4"/>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9" ht="18">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
         <v>56</v>
       </c>
@@ -1308,7 +1304,7 @@
       <c r="G12" s="4"/>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9" ht="18">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" s="6" t="s">
         <v>57</v>
       </c>
@@ -1321,7 +1317,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9" ht="18">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" s="6" t="s">
         <v>29</v>
       </c>
@@ -1336,7 +1332,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9" ht="18">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A15" s="6" t="s">
         <v>58</v>
       </c>
@@ -1347,7 +1343,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="18">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" s="6" t="s">
         <v>59</v>
       </c>
@@ -1359,7 +1355,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" s="6" t="s">
         <v>60</v>
       </c>
@@ -1370,7 +1366,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" s="6" t="s">
         <v>61</v>
       </c>
@@ -1381,20 +1377,20 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="18">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" s="6"/>
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="18">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" s="6"/>
     </row>
-    <row r="21" spans="1:4" ht="18">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" s="6"/>
     </row>
-    <row r="22" spans="1:4" ht="18">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" s="6"/>
     </row>
-    <row r="23" spans="1:4" ht="18">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" s="6"/>
     </row>
   </sheetData>
@@ -1406,14 +1402,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="7.1328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.125" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>71</v>
       </c>
@@ -1430,7 +1426,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" s="8">
         <v>22</v>
       </c>
@@ -1441,7 +1437,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="8">
         <v>23</v>
       </c>
@@ -1452,7 +1448,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" s="8">
         <v>24</v>
       </c>
@@ -1463,7 +1459,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="8">
         <v>25</v>
       </c>
@@ -1474,7 +1470,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" s="8">
         <v>26</v>
       </c>
@@ -1485,7 +1481,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B11" s="8" t="s">
         <v>21</v>
       </c>
@@ -1498,18 +1494,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00DA8846-409D-4B70-B280-9B5D3F94AB77}">
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
-    <col min="2" max="2" width="11.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.625" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="9" style="4"/>
     <col min="7" max="7" width="13" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="12"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="13"/>
       <c r="B1" s="13" t="s">
         <v>78</v>
@@ -1521,7 +1517,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
         <v>79</v>
       </c>
@@ -1529,16 +1525,10 @@
         <v>86</v>
       </c>
       <c r="C2" s="13">
-        <v>10</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="H2" s="12">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="13" t="s">
         <v>80</v>
       </c>
@@ -1548,74 +1538,98 @@
       <c r="C3" s="13">
         <v>50</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="H3" s="12">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
         <v>81</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C4" s="13">
         <v>200</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="H4" s="12">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
         <v>82</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C5" s="13">
         <v>500</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>83</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C6" s="13">
         <v>1000</v>
       </c>
-      <c r="G6" s="4" t="s">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="12">
+        <v>1000</v>
+      </c>
+      <c r="C10" s="4">
+        <v>12000</v>
+      </c>
+      <c r="G10" s="4">
+        <v>40700</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="12">
+        <v>2000</v>
+      </c>
+      <c r="C11" s="4">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="11"/>
+      <c r="B12" s="12"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="B14" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="4">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="G7" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="B10" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FA989B-8E8D-4FB9-A175-1A051FF98F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D49D994F-C8B6-4B66-BF43-D723F70BDC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>
@@ -23,23 +23,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="107">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -482,10 +471,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>药费</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>0~100</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -498,22 +483,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>柴火</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>粮食</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>衣服</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>随礼</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -586,8 +555,22 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <r>
-      <t>200</t>
+    <t>每两个节气</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>每个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节</t>
     </r>
     <r>
       <rPr>
@@ -595,28 +578,117 @@
         <color theme="1"/>
         <rFont val="Noto Sans JP"/>
         <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>~</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>400</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>300~2000</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>888~8888</t>
+        <charset val="134"/>
+      </rPr>
+      <t>气</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>立冬</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>立春，立夏，立秋</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小满，芒种，夏至，小暑</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>材发</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>霉</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>春分，秋分，大寒</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30%概率</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>修缮房屋</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>扫墓祭祖</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>清明，处暑</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>食物</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>煤炭</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人情随礼</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>每个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>气30%概率</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>布匹棉衣</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -624,17 +696,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -663,14 +735,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Noto Sans JP"/>
+      <name val="Microsoft YaHei UI"/>
       <family val="2"/>
-      <charset val="128"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Microsoft YaHei UI"/>
+      <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -710,7 +782,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -734,7 +806,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -742,7 +813,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1021,17 +1092,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="5.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.265625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.46484375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1048,7 +1119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="18">
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1062,7 +1133,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="18">
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1076,7 +1147,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="18">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1090,7 +1161,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="18">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1107,7 +1178,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" ht="18">
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
@@ -1130,16 +1201,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CE6F5-4C98-4917-9759-7DA81A6E4796}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="7" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1328125" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" ht="18">
       <c r="A1" s="6" t="s">
         <v>71</v>
       </c>
@@ -1153,7 +1224,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" ht="18">
       <c r="A2" s="6" t="s">
         <v>24</v>
       </c>
@@ -1167,7 +1238,7 @@
       <c r="G2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="18">
       <c r="A3" s="6" t="s">
         <v>25</v>
       </c>
@@ -1181,7 +1252,7 @@
       <c r="G3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" ht="18">
       <c r="A4" s="6" t="s">
         <v>26</v>
       </c>
@@ -1195,7 +1266,7 @@
       <c r="G4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" ht="18">
       <c r="A5" s="6" t="s">
         <v>27</v>
       </c>
@@ -1209,7 +1280,7 @@
       <c r="G5" s="4"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" ht="18">
       <c r="A6" s="6" t="s">
         <v>41</v>
       </c>
@@ -1222,7 +1293,7 @@
       <c r="D6" s="8"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" ht="18">
       <c r="A7" s="6" t="s">
         <v>42</v>
       </c>
@@ -1235,7 +1306,7 @@
       <c r="G7" s="4"/>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="18">
       <c r="A8" s="6" t="s">
         <v>43</v>
       </c>
@@ -1248,7 +1319,7 @@
       <c r="G8" s="4"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" ht="18">
       <c r="A9" s="6" t="s">
         <v>44</v>
       </c>
@@ -1261,7 +1332,7 @@
       <c r="G9" s="4"/>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" ht="18">
       <c r="A10" s="6" t="s">
         <v>45</v>
       </c>
@@ -1274,7 +1345,7 @@
       <c r="G10" s="4"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" ht="18">
       <c r="A11" s="6" t="s">
         <v>28</v>
       </c>
@@ -1290,7 +1361,7 @@
       <c r="G11" s="4"/>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" ht="18">
       <c r="A12" s="6" t="s">
         <v>56</v>
       </c>
@@ -1304,7 +1375,7 @@
       <c r="G12" s="4"/>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" ht="18">
       <c r="A13" s="6" t="s">
         <v>57</v>
       </c>
@@ -1317,7 +1388,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" ht="18">
       <c r="A14" s="6" t="s">
         <v>29</v>
       </c>
@@ -1332,7 +1403,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" ht="18">
       <c r="A15" s="6" t="s">
         <v>58</v>
       </c>
@@ -1343,7 +1414,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:9" ht="18">
       <c r="A16" s="6" t="s">
         <v>59</v>
       </c>
@@ -1355,7 +1426,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" ht="18">
       <c r="A17" s="6" t="s">
         <v>60</v>
       </c>
@@ -1366,7 +1437,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" ht="18">
       <c r="A18" s="6" t="s">
         <v>61</v>
       </c>
@@ -1377,20 +1448,20 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" ht="18">
       <c r="A19" s="6"/>
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" ht="18">
       <c r="A20" s="6"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" ht="18">
       <c r="A21" s="6"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" ht="18">
       <c r="A22" s="6"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" ht="18">
       <c r="A23" s="6"/>
     </row>
   </sheetData>
@@ -1402,14 +1473,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="7.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1328125" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5">
       <c r="A1" s="8" t="s">
         <v>71</v>
       </c>
@@ -1426,7 +1497,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5">
       <c r="A2" s="8">
         <v>22</v>
       </c>
@@ -1437,7 +1508,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5">
       <c r="A3" s="8">
         <v>23</v>
       </c>
@@ -1448,7 +1519,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5">
       <c r="A4" s="8">
         <v>24</v>
       </c>
@@ -1459,7 +1530,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5">
       <c r="A5" s="8">
         <v>25</v>
       </c>
@@ -1470,7 +1541,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5">
       <c r="A6" s="8">
         <v>26</v>
       </c>
@@ -1481,7 +1552,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5">
       <c r="B11" s="8" t="s">
         <v>21</v>
       </c>
@@ -1494,141 +1565,227 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00DA8846-409D-4B70-B280-9B5D3F94AB77}">
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="9" style="4"/>
-    <col min="2" max="2" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.9296875" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="9" style="4"/>
-    <col min="7" max="7" width="13" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" style="12"/>
+    <col min="7" max="7" width="8.6640625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="9" style="11"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="12"/>
+      <c r="B1" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="C2" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="13">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B3" s="13" t="s">
+      <c r="C3" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="12">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="12">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="13">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" s="13" t="s">
+      <c r="B10" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="4">
+        <v>188</v>
+      </c>
+      <c r="D12" s="4">
+        <v>288</v>
+      </c>
+      <c r="E12" s="4">
+        <v>588</v>
+      </c>
+      <c r="F12" s="4">
+        <v>688</v>
+      </c>
+      <c r="G12" s="11">
+        <v>888</v>
+      </c>
+      <c r="H12" s="4">
+        <v>1888</v>
+      </c>
+      <c r="I12" s="4">
+        <v>2888</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="13">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B5" s="13" t="s">
+      <c r="C13" s="4">
+        <v>300</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="4">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" s="4">
+        <v>800</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E15" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F15" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E16" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F16" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="13">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="13">
+      <c r="C17" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" s="4">
         <v>1000</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B10" s="12">
-        <v>1000</v>
-      </c>
-      <c r="C10" s="4">
-        <v>12000</v>
-      </c>
-      <c r="G10" s="4">
-        <v>40700</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="12">
+      <c r="E17" s="4">
         <v>2000</v>
       </c>
-      <c r="C11" s="4">
-        <v>24000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="4">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C14" s="4">
-        <v>2900</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>98</v>
+      <c r="F17" s="4">
+        <v>3000</v>
+      </c>
+      <c r="G17" s="4">
+        <v>4000</v>
+      </c>
+      <c r="H17" s="11">
+        <v>5000</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D49D994F-C8B6-4B66-BF43-D723F70BDC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1093E0-07A1-4AF8-B237-C3096C9B7DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1093E0-07A1-4AF8-B237-C3096C9B7DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4285BCC-6B13-4E05-9A7B-DA65CA985E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>
@@ -23,12 +23,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="109">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -159,10 +170,6 @@
   </si>
   <si>
     <t>肺气虚</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>心气虚</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -689,6 +696,18 @@
   </si>
   <si>
     <t>布匹棉衣</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -700,13 +719,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -813,7 +832,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1092,17 +1111,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="5.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.25" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.46484375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1119,7 +1138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18">
+    <row r="2" spans="1:5">
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1133,7 +1152,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18">
+    <row r="3" spans="1:5">
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1147,7 +1166,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18">
+    <row r="4" spans="1:5">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1161,7 +1180,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1178,7 +1197,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18">
+    <row r="6" spans="1:5">
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
@@ -1201,35 +1220,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CE6F5-4C98-4917-9759-7DA81A6E4796}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="7" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1328125" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18">
+    <row r="1" spans="1:9">
       <c r="A1" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="18">
+      <c r="E1" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" s="8">
         <v>36</v>
@@ -1238,26 +1266,29 @@
       <c r="G2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" ht="18">
+    <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="8">
         <v>55</v>
       </c>
       <c r="D3" s="5"/>
+      <c r="F3">
+        <v>1000</v>
+      </c>
       <c r="G3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" ht="18">
+    <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" s="8">
         <v>92</v>
@@ -1266,12 +1297,12 @@
       <c r="G4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" ht="18">
+    <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="8">
         <v>76</v>
@@ -1280,188 +1311,191 @@
       <c r="G5" s="4"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9" ht="18">
+    <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D6" s="8"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:9" ht="18">
+    <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G7" s="4"/>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9" ht="18">
+    <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G8" s="4"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" ht="18">
+    <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G9" s="4"/>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:9" ht="18">
+    <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G10" s="4"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:9" ht="18">
+    <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="8">
         <v>78</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G11" s="4"/>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9" ht="18">
+    <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G12" s="4"/>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9" ht="18">
+    <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9" ht="18">
+    <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="8">
         <v>103</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9" ht="18">
+    <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B16" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="18">
-      <c r="A16" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18">
-      <c r="A17" s="6" t="s">
+    <row r="18" spans="1:6">
+      <c r="A18" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B18" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D18" s="8" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="18">
-      <c r="A18" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="18">
+      <c r="F18">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="6"/>
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="18">
+    <row r="20" spans="1:6">
       <c r="A20" s="6"/>
     </row>
-    <row r="21" spans="1:4" ht="18">
+    <row r="21" spans="1:6">
       <c r="A21" s="6"/>
     </row>
-    <row r="22" spans="1:4" ht="18">
+    <row r="22" spans="1:6">
       <c r="A22" s="6"/>
     </row>
-    <row r="23" spans="1:4" ht="18">
+    <row r="23" spans="1:6">
       <c r="A23" s="6"/>
     </row>
   </sheetData>
@@ -1472,43 +1506,52 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.1328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.125" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:8">
       <c r="A1" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>74</v>
-      </c>
       <c r="E1" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>76</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="8">
         <v>22</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" s="8">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:8">
       <c r="A3" s="8">
         <v>23</v>
       </c>
@@ -1519,42 +1562,40 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:8">
       <c r="A4" s="8">
         <v>24</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4" s="8">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="D4" s="8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="8">
         <v>25</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="8">
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:8">
       <c r="A6" s="8">
         <v>26</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="8">
         <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="B11" s="8" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1568,10 +1609,10 @@
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="12.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.875" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="9" style="4"/>
-    <col min="7" max="7" width="8.6640625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="8.625" style="4" customWidth="1"/>
     <col min="8" max="8" width="9" style="11"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
@@ -1579,18 +1620,18 @@
     <row r="1" spans="1:9">
       <c r="A1" s="12"/>
       <c r="B1" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C2" s="12">
         <v>20</v>
@@ -1598,10 +1639,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" s="12">
         <v>50</v>
@@ -1609,10 +1650,10 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C4" s="12">
         <v>200</v>
@@ -1620,10 +1661,10 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C5" s="12">
         <v>500</v>
@@ -1631,10 +1672,10 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6" s="12">
         <v>1000</v>
@@ -1642,10 +1683,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C10" s="4">
         <v>1000</v>
@@ -1653,10 +1694,10 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C11" s="4">
         <v>1000</v>
@@ -1664,10 +1705,10 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="C12" s="4">
         <v>188</v>
@@ -1693,16 +1734,16 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C13" s="4">
         <v>300</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E13" s="4">
         <v>1200</v>
@@ -1710,16 +1751,16 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C14" s="4">
         <v>800</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E14" s="4">
         <v>2000</v>
@@ -1727,13 +1768,13 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="D15" s="4">
         <v>1000</v>
@@ -1747,10 +1788,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>100</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>101</v>
       </c>
       <c r="D16" s="4">
         <v>1000</v>
@@ -1764,13 +1805,13 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D17" s="4">
         <v>1000</v>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4285BCC-6B13-4E05-9A7B-DA65CA985E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50DB2AEC-7C40-4183-A7F4-0373DC071CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>
@@ -1606,7 +1606,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00DA8846-409D-4B70-B280-9B5D3F94AB77}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="12.875" style="4" bestFit="1" customWidth="1"/>
@@ -1617,7 +1617,7 @@
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:12">
       <c r="A1" s="12"/>
       <c r="B1" s="12" t="s">
         <v>77</v>
@@ -1626,7 +1626,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:12">
       <c r="A2" s="13" t="s">
         <v>78</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:12">
       <c r="A3" s="12" t="s">
         <v>79</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:12">
       <c r="A4" s="12" t="s">
         <v>80</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:12">
       <c r="A5" s="12" t="s">
         <v>81</v>
       </c>
@@ -1670,7 +1670,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:12">
       <c r="A6" s="12" t="s">
         <v>82</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:12">
       <c r="A10" s="4" t="s">
         <v>86</v>
       </c>
@@ -1691,8 +1691,11 @@
       <c r="C10" s="4">
         <v>1000</v>
       </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="L10" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="4" t="s">
         <v>101</v>
       </c>
@@ -1702,8 +1705,11 @@
       <c r="C11" s="4">
         <v>1000</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="L11" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="4" t="s">
         <v>103</v>
       </c>
@@ -1731,8 +1737,11 @@
       <c r="I12" s="4">
         <v>2888</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="L12" s="4">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="4" t="s">
         <v>102</v>
       </c>
@@ -1748,8 +1757,11 @@
       <c r="E13" s="4">
         <v>1200</v>
       </c>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="L13" s="4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="4" t="s">
         <v>105</v>
       </c>
@@ -1765,8 +1777,11 @@
       <c r="E14" s="4">
         <v>2000</v>
       </c>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="L14" s="4">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="4" t="s">
         <v>98</v>
       </c>
@@ -1785,8 +1800,11 @@
       <c r="F15" s="4">
         <v>3000</v>
       </c>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="L15" s="4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="4" t="s">
         <v>99</v>
       </c>
@@ -1802,8 +1820,11 @@
       <c r="F16" s="4">
         <v>3000</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="L16" s="4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="4" t="s">
         <v>95</v>
       </c>
@@ -1827,6 +1848,9 @@
       </c>
       <c r="H17" s="11">
         <v>5000</v>
+      </c>
+      <c r="L17" s="4">
+        <v>225</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -1,45 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50DB2AEC-7C40-4183-A7F4-0373DC071CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56AC192-D52A-43DF-A80A-2732B75692FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>
     <sheet name="赈灾药材案" sheetId="2" r:id="rId2"/>
     <sheet name="支线剧情" sheetId="3" r:id="rId3"/>
     <sheet name="收入" sheetId="4" r:id="rId4"/>
+    <sheet name="音乐" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="113">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -709,23 +699,37 @@
   <si>
     <t>奖励心得</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>春：竹笛《春到湘江》</t>
+  </si>
+  <si>
+    <t>夏：琵琶《月儿高》</t>
+  </si>
+  <si>
+    <t>秋：洞箫《平沙落雁》</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>冬：古琴《梅花三弄》</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -765,6 +769,30 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -801,7 +829,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -830,9 +858,11 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1111,17 +1141,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="5.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.265625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.46484375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" ht="18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1138,7 +1168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" ht="18">
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1152,7 +1182,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" ht="18">
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1166,7 +1196,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" ht="18">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1180,7 +1210,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="18">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1197,7 +1227,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" ht="18">
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
@@ -1220,16 +1250,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CE6F5-4C98-4917-9759-7DA81A6E4796}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="7" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1328125" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" ht="18">
       <c r="A1" s="6" t="s">
         <v>70</v>
       </c>
@@ -1252,7 +1282,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" ht="18">
       <c r="A2" s="6" t="s">
         <v>23</v>
       </c>
@@ -1266,7 +1296,7 @@
       <c r="G2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" ht="18">
       <c r="A3" s="6" t="s">
         <v>24</v>
       </c>
@@ -1283,7 +1313,7 @@
       <c r="G3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" ht="18">
       <c r="A4" s="6" t="s">
         <v>25</v>
       </c>
@@ -1297,7 +1327,7 @@
       <c r="G4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" ht="18">
       <c r="A5" s="6" t="s">
         <v>26</v>
       </c>
@@ -1311,7 +1341,7 @@
       <c r="G5" s="4"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" ht="18">
       <c r="A6" s="6" t="s">
         <v>40</v>
       </c>
@@ -1324,7 +1354,7 @@
       <c r="D6" s="8"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" ht="18">
       <c r="A7" s="6" t="s">
         <v>41</v>
       </c>
@@ -1337,7 +1367,7 @@
       <c r="G7" s="4"/>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" ht="18">
       <c r="A8" s="6" t="s">
         <v>42</v>
       </c>
@@ -1350,7 +1380,7 @@
       <c r="G8" s="4"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" ht="18">
       <c r="A9" s="6" t="s">
         <v>43</v>
       </c>
@@ -1363,7 +1393,7 @@
       <c r="G9" s="4"/>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" ht="18">
       <c r="A10" s="6" t="s">
         <v>44</v>
       </c>
@@ -1376,7 +1406,7 @@
       <c r="G10" s="4"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" ht="18">
       <c r="A11" s="6" t="s">
         <v>27</v>
       </c>
@@ -1392,7 +1422,7 @@
       <c r="G11" s="4"/>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" ht="18">
       <c r="A12" s="6" t="s">
         <v>55</v>
       </c>
@@ -1406,7 +1436,7 @@
       <c r="G12" s="4"/>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" ht="18">
       <c r="A13" s="6" t="s">
         <v>56</v>
       </c>
@@ -1419,7 +1449,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" ht="18">
       <c r="A14" s="6" t="s">
         <v>28</v>
       </c>
@@ -1434,7 +1464,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" ht="18">
       <c r="A15" s="6" t="s">
         <v>57</v>
       </c>
@@ -1445,7 +1475,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" ht="18">
       <c r="A16" s="6" t="s">
         <v>58</v>
       </c>
@@ -1457,7 +1487,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" ht="18">
       <c r="A17" s="6" t="s">
         <v>59</v>
       </c>
@@ -1468,7 +1498,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" ht="18">
       <c r="A18" s="6" t="s">
         <v>60</v>
       </c>
@@ -1482,20 +1512,20 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" ht="18">
       <c r="A19" s="6"/>
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" ht="18">
       <c r="A20" s="6"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" ht="18">
       <c r="A21" s="6"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" ht="18">
       <c r="A22" s="6"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" ht="18">
       <c r="A23" s="6"/>
     </row>
   </sheetData>
@@ -1507,9 +1537,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="7.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1328125" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
@@ -1606,18 +1636,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00DA8846-409D-4B70-B280-9B5D3F94AB77}">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="12.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.86328125" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="9" style="4"/>
-    <col min="7" max="7" width="8.625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="8.59765625" style="4" customWidth="1"/>
     <col min="8" max="8" width="9" style="11"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:9">
       <c r="A1" s="12"/>
       <c r="B1" s="12" t="s">
         <v>77</v>
@@ -1626,7 +1656,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:9">
       <c r="A2" s="13" t="s">
         <v>78</v>
       </c>
@@ -1637,7 +1667,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:9">
       <c r="A3" s="12" t="s">
         <v>79</v>
       </c>
@@ -1648,7 +1678,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:9">
       <c r="A4" s="12" t="s">
         <v>80</v>
       </c>
@@ -1659,7 +1689,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:9">
       <c r="A5" s="12" t="s">
         <v>81</v>
       </c>
@@ -1670,7 +1700,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:9">
       <c r="A6" s="12" t="s">
         <v>82</v>
       </c>
@@ -1681,7 +1711,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
         <v>86</v>
       </c>
@@ -1691,11 +1721,8 @@
       <c r="C10" s="4">
         <v>1000</v>
       </c>
-      <c r="L10" s="4">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
         <v>101</v>
       </c>
@@ -1705,11 +1732,8 @@
       <c r="C11" s="4">
         <v>1000</v>
       </c>
-      <c r="L11" s="4">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
         <v>103</v>
       </c>
@@ -1737,11 +1761,8 @@
       <c r="I12" s="4">
         <v>2888</v>
       </c>
-      <c r="L12" s="4">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
         <v>102</v>
       </c>
@@ -1757,11 +1778,8 @@
       <c r="E13" s="4">
         <v>1200</v>
       </c>
-      <c r="L13" s="4">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
         <v>105</v>
       </c>
@@ -1777,11 +1795,8 @@
       <c r="E14" s="4">
         <v>2000</v>
       </c>
-      <c r="L14" s="4">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="4" t="s">
         <v>98</v>
       </c>
@@ -1800,11 +1815,8 @@
       <c r="F15" s="4">
         <v>3000</v>
       </c>
-      <c r="L15" s="4">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="4" t="s">
         <v>99</v>
       </c>
@@ -1820,11 +1832,8 @@
       <c r="F16" s="4">
         <v>3000</v>
       </c>
-      <c r="L16" s="4">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
         <v>95</v>
       </c>
@@ -1848,9 +1857,6 @@
       </c>
       <c r="H17" s="11">
         <v>5000</v>
-      </c>
-      <c r="L17" s="4">
-        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -1858,4 +1864,35 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA86077C-61A9-404C-B3A5-652B97F71E5C}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="14" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56AC192-D52A-43DF-A80A-2732B75692FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D8FC150-2E16-475F-BD48-D403188D83D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>
@@ -24,12 +24,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="115">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -713,6 +724,14 @@
   <si>
     <t>冬：古琴《梅花三弄》</t>
     <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>田租</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>俸禄</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -723,13 +742,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -773,13 +792,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -788,7 +807,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -862,7 +881,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1141,17 +1160,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="5.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.25" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.46484375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1168,7 +1187,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18">
+    <row r="2" spans="1:5">
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1182,7 +1201,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18">
+    <row r="3" spans="1:5">
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1196,7 +1215,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18">
+    <row r="4" spans="1:5">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1210,7 +1229,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1227,7 +1246,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18">
+    <row r="6" spans="1:5">
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
@@ -1250,16 +1269,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CE6F5-4C98-4917-9759-7DA81A6E4796}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="7" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.125" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18">
+    <row r="1" spans="1:9">
       <c r="A1" s="6" t="s">
         <v>70</v>
       </c>
@@ -1282,7 +1301,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="18">
+    <row r="2" spans="1:9">
       <c r="A2" s="6" t="s">
         <v>23</v>
       </c>
@@ -1296,7 +1315,7 @@
       <c r="G2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" ht="18">
+    <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>24</v>
       </c>
@@ -1313,7 +1332,7 @@
       <c r="G3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" ht="18">
+    <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>25</v>
       </c>
@@ -1327,7 +1346,7 @@
       <c r="G4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" ht="18">
+    <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>26</v>
       </c>
@@ -1341,7 +1360,7 @@
       <c r="G5" s="4"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9" ht="18">
+    <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>40</v>
       </c>
@@ -1354,7 +1373,7 @@
       <c r="D6" s="8"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:9" ht="18">
+    <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>41</v>
       </c>
@@ -1367,7 +1386,7 @@
       <c r="G7" s="4"/>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9" ht="18">
+    <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>42</v>
       </c>
@@ -1380,7 +1399,7 @@
       <c r="G8" s="4"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" ht="18">
+    <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>43</v>
       </c>
@@ -1393,7 +1412,7 @@
       <c r="G9" s="4"/>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:9" ht="18">
+    <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>44</v>
       </c>
@@ -1406,7 +1425,7 @@
       <c r="G10" s="4"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:9" ht="18">
+    <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>27</v>
       </c>
@@ -1422,7 +1441,7 @@
       <c r="G11" s="4"/>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9" ht="18">
+    <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>55</v>
       </c>
@@ -1436,7 +1455,7 @@
       <c r="G12" s="4"/>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9" ht="18">
+    <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>56</v>
       </c>
@@ -1449,7 +1468,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9" ht="18">
+    <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>28</v>
       </c>
@@ -1464,7 +1483,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9" ht="18">
+    <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>57</v>
       </c>
@@ -1475,7 +1494,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="18">
+    <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>58</v>
       </c>
@@ -1487,7 +1506,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="18">
+    <row r="17" spans="1:6">
       <c r="A17" s="6" t="s">
         <v>59</v>
       </c>
@@ -1498,7 +1517,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="18">
+    <row r="18" spans="1:6">
       <c r="A18" s="6" t="s">
         <v>60</v>
       </c>
@@ -1512,20 +1531,20 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="18">
+    <row r="19" spans="1:6">
       <c r="A19" s="6"/>
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="1:6" ht="18">
+    <row r="20" spans="1:6">
       <c r="A20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="18">
+    <row r="21" spans="1:6">
       <c r="A21" s="6"/>
     </row>
-    <row r="22" spans="1:6" ht="18">
+    <row r="22" spans="1:6">
       <c r="A22" s="6"/>
     </row>
-    <row r="23" spans="1:6" ht="18">
+    <row r="23" spans="1:6">
       <c r="A23" s="6"/>
     </row>
   </sheetData>
@@ -1537,9 +1556,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.1328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.125" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
@@ -1639,10 +1658,10 @@
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="12.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.875" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="9" style="4"/>
-    <col min="7" max="7" width="8.59765625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="8.625" style="4" customWidth="1"/>
     <col min="8" max="8" width="9" style="11"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
@@ -1709,6 +1728,22 @@
       </c>
       <c r="C6" s="12">
         <v>1000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="4">
+        <v>2000</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1869,7 +1904,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA86077C-61A9-404C-B3A5-652B97F71E5C}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="14" t="s">

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D8FC150-2E16-475F-BD48-D403188D83D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7051110-7705-4773-8CC3-853C777F69D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>
@@ -399,8 +399,327 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <r>
-      <t>107全解</t>
+    <t>013+1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>015+3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>解锁心得</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前置剧情</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>肺阴虚</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>温燥证</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>天数</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名望</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初窥门径</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>略有小成</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>融会贯通</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>炉火纯青</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出神入化</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>诊费</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0~100</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>101~300</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>陈皮半夏工钱</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1~</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>301~</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>600</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1~</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2000</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>每两个节气</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>每个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>气</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>立冬</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>立春，立夏，立秋</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小满，芒种，夏至，小暑</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>材发</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>霉</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>春分，秋分，大寒</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30%概率</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>修缮房屋</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>扫墓祭祖</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>清明，处暑</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>食物</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>煤炭</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人情随礼</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>每个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>节</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>气30%概率</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>布匹棉衣</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>春：竹笛《春到湘江》</t>
+  </si>
+  <si>
+    <t>夏：琵琶《月儿高》</t>
+  </si>
+  <si>
+    <t>秋：洞箫《平沙落雁》</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>冬：古琴《梅花三弄》</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>田租</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>俸禄</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>全解</t>
     </r>
     <r>
       <rPr>
@@ -412,325 +731,6 @@
       </rPr>
       <t>锁</t>
     </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>013+1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>015+3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>剧情ID</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>剧情名</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>解锁心得</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>前置剧情</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>肺阴虚</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>温燥证</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>天数</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>名望</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>初窥门径</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>略有小成</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>融会贯通</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>炉火纯青</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>出神入化</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>诊费</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>0~100</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>101~300</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>陈皮半夏工钱</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1~</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>301~</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>600</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1~</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2000</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>每两个节气</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>每个</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>节</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>气</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>立冬</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>立春，立夏，立秋</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>小满，芒种，夏至，小暑</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>药</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>材发</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>霉</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>春分，秋分，大寒</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>30%概率</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>修缮房屋</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>扫墓祭祖</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>清明，处暑</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>食物</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>煤炭</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>人情随礼</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>每个</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>节</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>气30%概率</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>布匹棉衣</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>奖励金钱</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>奖励名望</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>奖励心得</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>春：竹笛《春到湘江》</t>
-  </si>
-  <si>
-    <t>夏：琵琶《月儿高》</t>
-  </si>
-  <si>
-    <t>秋：洞箫《平沙落雁》</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>冬：古琴《梅花三弄》</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>田租</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>俸禄</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1280,25 +1280,25 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>73</v>
-      </c>
       <c r="E1" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1368,7 +1368,7 @@
         <v>35</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="D6" s="8"/>
       <c r="G6" s="4"/>
@@ -1436,7 +1436,7 @@
         <v>78</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G11" s="4"/>
       <c r="I11" s="4"/>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I13" s="4"/>
     </row>
@@ -1555,7 +1555,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="7.125" style="8" bestFit="1" customWidth="1"/>
@@ -1563,44 +1563,44 @@
     <col min="3" max="4" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:11">
       <c r="A1" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>73</v>
-      </c>
       <c r="E1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F1" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="8">
         <v>22</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" s="8">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:11">
       <c r="A3" s="8">
         <v>23</v>
       </c>
@@ -1611,12 +1611,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:11">
       <c r="A4" s="8">
         <v>24</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C4" s="8">
         <v>44</v>
@@ -1624,8 +1624,11 @@
       <c r="D4" s="8">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="K4" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="8">
         <v>25</v>
       </c>
@@ -1635,8 +1638,11 @@
       <c r="C5" s="8">
         <v>98</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="K5" s="8">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="8">
         <v>26</v>
       </c>
@@ -1644,6 +1650,39 @@
         <v>22</v>
       </c>
       <c r="C6" s="8">
+        <v>105</v>
+      </c>
+      <c r="K6" s="8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="K7" s="8">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="K8" s="8">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="K9" s="8">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="K10" s="8">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="K11" s="8">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="K12" s="8">
         <v>105</v>
       </c>
     </row>
@@ -1669,18 +1708,18 @@
     <row r="1" spans="1:9">
       <c r="A1" s="12"/>
       <c r="B1" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" s="12">
         <v>20</v>
@@ -1688,10 +1727,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C3" s="12">
         <v>50</v>
@@ -1699,10 +1738,10 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C4" s="12">
         <v>200</v>
@@ -1710,10 +1749,10 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" s="12">
         <v>500</v>
@@ -1721,10 +1760,10 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" s="12">
         <v>1000</v>
@@ -1732,7 +1771,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B7" s="4">
         <v>20000</v>
@@ -1740,7 +1779,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B8" s="4">
         <v>2000</v>
@@ -1748,10 +1787,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" s="4">
         <v>1000</v>
@@ -1759,10 +1798,10 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" s="4">
         <v>1000</v>
@@ -1770,10 +1809,10 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>104</v>
       </c>
       <c r="C12" s="4">
         <v>188</v>
@@ -1799,16 +1838,16 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C13" s="4">
         <v>300</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E13" s="4">
         <v>1200</v>
@@ -1816,16 +1855,16 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C14" s="4">
         <v>800</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E14" s="4">
         <v>2000</v>
@@ -1833,13 +1872,13 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="D15" s="4">
         <v>1000</v>
@@ -1853,10 +1892,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>99</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>100</v>
       </c>
       <c r="D16" s="4">
         <v>1000</v>
@@ -1870,13 +1909,13 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D17" s="4">
         <v>1000</v>
@@ -1908,22 +1947,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7051110-7705-4773-8CC3-853C777F69D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF289CB9-4F07-4F09-9EDE-52704B838531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>
-    <sheet name="赈灾药材案" sheetId="2" r:id="rId2"/>
-    <sheet name="支线剧情" sheetId="3" r:id="rId3"/>
-    <sheet name="收入" sheetId="4" r:id="rId4"/>
-    <sheet name="音乐" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId2"/>
+    <sheet name="赈灾药材案" sheetId="2" r:id="rId3"/>
+    <sheet name="支线剧情" sheetId="3" r:id="rId4"/>
+    <sheet name="收入" sheetId="4" r:id="rId5"/>
+    <sheet name="音乐" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="136">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -731,6 +732,90 @@
       </rPr>
       <t>锁</t>
     </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鸟叫</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>蟋蟀青蛙</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>猫头鹰</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>乌鸦</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>树叶摩挲</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒风</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>小</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>大</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>蝉鸣</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>022</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>023</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>024</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>025</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>元宵灯节</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>主线剧情</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>000</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>004</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>老师心阳虚</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>心得</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -848,7 +933,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -879,6 +964,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1267,6 +1358,182 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD551C76-47E1-4A91-9FB6-46DD09A2A3A3}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="4.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="8">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="8">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="8">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="8">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="8">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="8">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="8">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="16"/>
+      <c r="B12" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="16"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="16"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="16"/>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="16"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CE6F5-4C98-4917-9759-7DA81A6E4796}">
   <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -1553,7 +1820,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -1624,9 +1891,7 @@
       <c r="D4" s="8">
         <v>23</v>
       </c>
-      <c r="K4" s="8">
-        <v>14</v>
-      </c>
+      <c r="K4" s="8"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="8">
@@ -1638,9 +1903,7 @@
       <c r="C5" s="8">
         <v>98</v>
       </c>
-      <c r="K5" s="8">
-        <v>36</v>
-      </c>
+      <c r="K5" s="8"/>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="8">
@@ -1652,39 +1915,28 @@
       <c r="C6" s="8">
         <v>105</v>
       </c>
-      <c r="K6" s="8">
-        <v>40</v>
-      </c>
+      <c r="K6" s="8"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="K7" s="8">
-        <v>44</v>
-      </c>
+      <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="K8" s="8">
-        <v>55</v>
-      </c>
+      <c r="K8" s="8"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="K9" s="8">
-        <v>76</v>
-      </c>
+      <c r="B9" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="K10" s="8">
-        <v>92</v>
-      </c>
+      <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="8">
-        <v>98</v>
-      </c>
+      <c r="K11" s="8"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="K12" s="8">
-        <v>105</v>
-      </c>
+      <c r="K12" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1692,7 +1944,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00DA8846-409D-4B70-B280-9B5D3F94AB77}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
@@ -1940,29 +2192,59 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA86077C-61A9-404C-B3A5-652B97F71E5C}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:6">
       <c r="A1" s="14" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="D1" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="14" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="3" spans="1:1">
+      <c r="D2" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="15" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="4" spans="1:1">
+      <c r="D3" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="15" t="s">
         <v>111</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF289CB9-4F07-4F09-9EDE-52704B838531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EFFACE2-701D-48F5-BBC7-12E800ADCBBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="141">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -816,6 +816,38 @@
   </si>
   <si>
     <t>心得</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>027</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上元灯节</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>009</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>027</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>辞别老</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>师</t>
+    </r>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1359,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD551C76-47E1-4A91-9FB6-46DD09A2A3A3}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.5" style="9" bestFit="1" customWidth="1"/>
@@ -1406,126 +1438,167 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="8">
-        <v>36</v>
+        <v>132</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="16" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="C5" s="8">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="C6" s="8">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="16" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="C7" s="8">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C8" s="8">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" s="8">
-        <v>92</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="8">
-        <v>98</v>
-      </c>
+      <c r="A10" s="16"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="16" t="s">
-        <v>128</v>
+        <v>25</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C11" s="8">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="16"/>
+      <c r="A12" s="16" t="s">
+        <v>127</v>
+      </c>
       <c r="B12" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>114</v>
+        <v>21</v>
+      </c>
+      <c r="C12" s="8">
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="E13" s="9">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="8">
+        <v>105</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="E14" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E15" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B16" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D16" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="16"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="16"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="16"/>
+      <c r="E16" s="9">
+        <v>2</v>
+      </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="16"/>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="16"/>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="16"/>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EFFACE2-701D-48F5-BBC7-12E800ADCBBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58455319-884E-4FD1-BB06-8A116E5C6A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="151">
   <si>
     <t>嘉靖</t>
     <phoneticPr fontId="1"/>
@@ -849,6 +849,42 @@
       <t>师</t>
     </r>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金钱</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名望</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>心得</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>024</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>王百堂来访</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>药商来访</t>
+  </si>
+  <si>
+    <t>柳敬亭温燥证</t>
+  </si>
+  <si>
+    <t>谢飞燕肺气虚</t>
+  </si>
+  <si>
+    <t>谢飞燕肺阴虚</t>
   </si>
 </sst>
 </file>
@@ -965,7 +1001,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1000,6 +1036,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1391,19 +1430,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD551C76-47E1-4A91-9FB6-46DD09A2A3A3}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.5" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.125" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="9"/>
+    <col min="3" max="3" width="5.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="9"/>
+    <col min="5" max="6" width="5.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:8">
       <c r="A1" s="8" t="s">
         <v>134</v>
       </c>
+      <c r="B1" s="8" t="s">
+        <v>144</v>
+      </c>
       <c r="C1" s="8" t="s">
         <v>135</v>
       </c>
@@ -1413,8 +1459,17 @@
       <c r="E1" s="8" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="16" t="s">
         <v>132</v>
       </c>
@@ -1424,19 +1479,22 @@
       <c r="E2" s="9">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="H2" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="16" t="s">
         <v>124</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="C3" s="8">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:8">
       <c r="A4" s="16" t="s">
         <v>132</v>
       </c>
@@ -1447,41 +1505,44 @@
       <c r="D4" s="16" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="E4" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="16" t="s">
         <v>23</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>30</v>
+        <v>147</v>
       </c>
       <c r="C5" s="8">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:8">
       <c r="A6" s="16" t="s">
         <v>125</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="C6" s="8">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:8">
       <c r="A7" s="16" t="s">
         <v>126</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="C7" s="8">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:8">
       <c r="A8" s="16" t="s">
         <v>24</v>
       </c>
@@ -1491,8 +1552,14 @@
       <c r="C8" s="8">
         <v>55</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="G8" s="9">
+        <v>1000</v>
+      </c>
+      <c r="H8" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="16" t="s">
         <v>26</v>
       </c>
@@ -1503,12 +1570,25 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="16"/>
-      <c r="B10" s="8"/>
+    <row r="10" spans="1:8">
+      <c r="A10" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>146</v>
+      </c>
       <c r="C10" s="8"/>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="D10" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="9">
+        <v>1</v>
+      </c>
+      <c r="H10" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="16" t="s">
         <v>25</v>
       </c>
@@ -1519,7 +1599,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:8">
       <c r="A12" s="16" t="s">
         <v>127</v>
       </c>
@@ -1530,7 +1610,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:8">
       <c r="A13" s="16" t="s">
         <v>136</v>
       </c>
@@ -1542,7 +1622,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:8">
       <c r="A14" s="16" t="s">
         <v>128</v>
       </c>
@@ -1559,7 +1639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:8">
       <c r="A15" s="16" t="s">
         <v>138</v>
       </c>
@@ -1574,7 +1654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:8">
       <c r="A16" s="16" t="s">
         <v>131</v>
       </c>

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58455319-884E-4FD1-BB06-8A116E5C6A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715EF0E1-D3E9-4543-93FF-8AB0D77B8AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1437,8 +1437,8 @@
     <col min="2" max="2" width="15.125" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.25" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="9"/>
-    <col min="5" max="6" width="5.25" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.5" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.25" style="9" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="9"/>
   </cols>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="18" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E10" s="9">
         <v>1</v>
@@ -1608,6 +1608,9 @@
       </c>
       <c r="C12" s="8">
         <v>98</v>
+      </c>
+      <c r="F12" s="9">
+        <v>2000</v>
       </c>
     </row>
     <row r="13" spans="1:8">

--- a/DataTables/剧情大纲.xlsx
+++ b/DataTables/剧情大纲.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715EF0E1-D3E9-4543-93FF-8AB0D77B8AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124395C8-0411-405B-AE02-0180CA53A338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="时间线" sheetId="1" r:id="rId1"/>
@@ -895,13 +895,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -945,13 +945,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -960,7 +960,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1043,7 +1043,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1322,17 +1322,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="5.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.265625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.46484375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" ht="18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" ht="18">
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" ht="18">
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" ht="18">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="18">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" ht="18">
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
@@ -1431,19 +1431,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD551C76-47E1-4A91-9FB6-46DD09A2A3A3}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="4.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.125" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.46484375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.265625" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="9"/>
-    <col min="5" max="5" width="5.25" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="5.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.265625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.46484375" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.265625" style="9" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" ht="18">
       <c r="A1" s="8" t="s">
         <v>134</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" ht="18">
       <c r="A2" s="16" t="s">
         <v>132</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" ht="18">
       <c r="A3" s="16" t="s">
         <v>124</v>
       </c>
@@ -1494,7 +1494,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" ht="18">
       <c r="A4" s="16" t="s">
         <v>132</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" ht="18">
       <c r="A5" s="16" t="s">
         <v>23</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" ht="18">
       <c r="A6" s="16" t="s">
         <v>125</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" ht="18">
       <c r="A7" s="16" t="s">
         <v>126</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" ht="18">
       <c r="A8" s="16" t="s">
         <v>24</v>
       </c>
@@ -1559,7 +1559,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" ht="18">
       <c r="A9" s="16" t="s">
         <v>26</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" ht="18">
       <c r="A10" s="16" t="s">
         <v>145</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" ht="18">
       <c r="A11" s="16" t="s">
         <v>25</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" ht="18">
       <c r="A12" s="16" t="s">
         <v>127</v>
       </c>
@@ -1613,7 +1613,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" ht="18">
       <c r="A13" s="16" t="s">
         <v>136</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" ht="18">
       <c r="A14" s="16" t="s">
         <v>128</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" ht="18">
       <c r="A15" s="16" t="s">
         <v>138</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" ht="18">
       <c r="A16" s="16" t="s">
         <v>131</v>
       </c>
@@ -1671,16 +1671,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" ht="18">
       <c r="A17" s="16"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" ht="18">
       <c r="A18" s="16"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" ht="18">
       <c r="A19" s="16"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" ht="18">
       <c r="A20" s="16"/>
     </row>
   </sheetData>
@@ -1692,16 +1692,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3CE6F5-4C98-4917-9759-7DA81A6E4796}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="7" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1328125" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" ht="18">
       <c r="A1" s="6" t="s">
         <v>69</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" ht="18">
       <c r="A2" s="6" t="s">
         <v>23</v>
       </c>
@@ -1738,7 +1738,7 @@
       <c r="G2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" ht="18">
       <c r="A3" s="6" t="s">
         <v>24</v>
       </c>
@@ -1755,7 +1755,7 @@
       <c r="G3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" ht="18">
       <c r="A4" s="6" t="s">
         <v>25</v>
       </c>
@@ -1769,7 +1769,7 @@
       <c r="G4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" ht="18">
       <c r="A5" s="6" t="s">
         <v>26</v>
       </c>
@@ -1783,7 +1783,7 @@
       <c r="G5" s="4"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" ht="18">
       <c r="A6" s="6" t="s">
         <v>40</v>
       </c>
@@ -1796,7 +1796,7 @@
       <c r="D6" s="8"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" ht="18">
       <c r="A7" s="6" t="s">
         <v>41</v>
       </c>
@@ -1809,7 +1809,7 @@
       <c r="G7" s="4"/>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" ht="18">
       <c r="A8" s="6" t="s">
         <v>42</v>
       </c>
@@ -1822,7 +1822,7 @@
       <c r="G8" s="4"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" ht="18">
       <c r="A9" s="6" t="s">
         <v>43</v>
       </c>
@@ -1835,7 +1835,7 @@
       <c r="G9" s="4"/>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" ht="18">
       <c r="A10" s="6" t="s">
         <v>44</v>
       </c>
@@ -1848,7 +1848,7 @@
       <c r="G10" s="4"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" ht="18">
       <c r="A11" s="6" t="s">
         <v>27</v>
       </c>
@@ -1864,7 +1864,7 @@
       <c r="G11" s="4"/>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" ht="18">
       <c r="A12" s="6" t="s">
         <v>55</v>
       </c>
@@ -1878,7 +1878,7 @@
       <c r="G12" s="4"/>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" ht="18">
       <c r="A13" s="6" t="s">
         <v>56</v>
       </c>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" ht="18">
       <c r="A14" s="6" t="s">
         <v>28</v>
       </c>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" ht="18">
       <c r="A15" s="6" t="s">
         <v>57</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" ht="18">
       <c r="A16" s="6" t="s">
         <v>58</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" ht="18">
       <c r="A17" s="6" t="s">
         <v>59</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" ht="18">
       <c r="A18" s="6" t="s">
         <v>60</v>
       </c>
@@ -1954,20 +1954,20 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" ht="18">
       <c r="A19" s="6"/>
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" ht="18">
       <c r="A20" s="6"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" ht="18">
       <c r="A21" s="6"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" ht="18">
       <c r="A22" s="6"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" ht="18">
       <c r="A23" s="6"/>
     </row>
   </sheetData>
@@ -1979,9 +1979,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA3626-9D35-4B08-8B66-BF275758C0A6}">
   <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="7.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1328125" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
@@ -2105,10 +2105,10 @@
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="12.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.86328125" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="9" style="4"/>
-    <col min="7" max="7" width="8.625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="8.59765625" style="4" customWidth="1"/>
     <col min="8" max="8" width="9" style="11"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
@@ -2351,9 +2351,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA86077C-61A9-404C-B3A5-652B97F71E5C}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="18">
       <c r="A1" s="14" t="s">
         <v>108</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" ht="18">
       <c r="A2" s="14" t="s">
         <v>109</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" ht="18">
       <c r="A3" s="15" t="s">
         <v>110</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" ht="18">
       <c r="A4" s="15" t="s">
         <v>111</v>
       </c>
